--- a/chem/Lab9_Gravimetric_Data.xlsx
+++ b/chem/Lab9_Gravimetric_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3aaf0ddacaed4ea8/Documents/CODE/CODE SUMMARY/chem/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_2B59BCBF10EF14749F5B6E72549230F34207EA4D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A467FCC5-37DB-476D-961F-A6CA2A678B49}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_2B59BCBF10EF14749F5B6E72549230F34207EA4D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E482179-AD59-4959-855A-246890E68A8B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -673,8 +673,12 @@
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
+      <c r="B10" s="5">
+        <v>1.405</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1.663</v>
+      </c>
     </row>
     <row r="12" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
@@ -700,11 +704,11 @@
       </c>
       <c r="B14" s="6">
         <f>B10-B9</f>
-        <v>-0.46899999999999997</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="C14" s="6">
         <f>C10-C9</f>
-        <v>-0.72799999999999998</v>
+        <v>0.93500000000000005</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -713,11 +717,11 @@
       </c>
       <c r="B15" s="7">
         <f>B14/143.32</f>
-        <v>-3.2723974323192856E-3</v>
+        <v>6.5308400781468054E-3</v>
       </c>
       <c r="C15" s="7">
         <f>C14/143.32</f>
-        <v>-5.07954228300307E-3</v>
+        <v>6.5238626849009216E-3</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -726,11 +730,11 @@
       </c>
       <c r="B16" s="6">
         <f>B15*35.45</f>
-        <v>-0.11600648897571869</v>
+        <v>0.23151828077030426</v>
       </c>
       <c r="C16" s="6">
         <f>C15*35.45</f>
-        <v>-0.18006977393245885</v>
+        <v>0.23127093217973768</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
@@ -739,11 +743,11 @@
       </c>
       <c r="B17" s="8">
         <f>B16/B8*100</f>
-        <v>-27.88617523454776</v>
+        <v>55.65343287747698</v>
       </c>
       <c r="C17" s="8">
         <f>C16/C8*100</f>
-        <v>-43.182199983803081</v>
+        <v>55.460655198977861</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="26" customHeight="1" x14ac:dyDescent="0.35">
@@ -752,7 +756,7 @@
       </c>
       <c r="B19" s="10">
         <f>AVERAGE(B17:C17)</f>
-        <v>-35.534187609175419</v>
+        <v>55.557044038227417</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>17</v>
